--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5395-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5395-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1D596B0-A739-4C41-9B16-934F7E11EC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9F7AF37-A1CB-49CE-BB24-CB27E5FC53AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{B041B3A2-AFB3-4F59-9067-95759EDEC99D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{9203A87D-E9B0-419B-ADD2-EC3580C82EAD}"/>
   </bookViews>
   <sheets>
     <sheet name="5395-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1424,24 +1424,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147A59DE-4C10-42ED-B4C0-B449FE8854D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751FC10C-A177-4959-A851-34A2AA690C1F}">
   <dimension ref="A1:X24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1475,7 +1474,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1511,7 +1510,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1563,7 +1562,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1631,7 +1630,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2015</v>
       </c>
@@ -1703,7 +1702,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2014</v>
       </c>
@@ -1775,7 +1774,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2013</v>
       </c>
@@ -1847,7 +1846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2012</v>
       </c>
@@ -1919,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2011</v>
       </c>
@@ -1991,7 +1990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2010</v>
       </c>
@@ -2063,7 +2062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2009</v>
       </c>
@@ -2135,7 +2134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2008</v>
       </c>
@@ -2207,7 +2206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2007</v>
       </c>
@@ -2279,7 +2278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2006</v>
       </c>
@@ -2351,7 +2350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2005</v>
       </c>
@@ -2423,7 +2422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2004</v>
       </c>
@@ -2495,7 +2494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2003</v>
       </c>
@@ -2567,7 +2566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2002</v>
       </c>
@@ -2639,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2001</v>
       </c>
@@ -2711,7 +2710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2000</v>
       </c>
@@ -2783,7 +2782,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>1999</v>
       </c>
@@ -2855,7 +2854,7 @@
         <v>9.7100000000000009</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>1998</v>
       </c>
@@ -2927,7 +2926,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>1997</v>
       </c>
@@ -2999,7 +2998,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="s">
         <v>34</v>
       </c>
